--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5034</v>
+        <v>5036</v>
       </c>
       <c r="Q2" t="n">
         <v>658</v>
       </c>
       <c r="R2" t="n">
-        <v>5692</v>
+        <v>5694</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="Q3" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="R3" t="n">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1000,10 +1000,10 @@
         <v>142</v>
       </c>
       <c r="Q6" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="R6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         <v>176</v>
       </c>
       <c r="Q7" t="n">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="R7" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jdaeun96@naver.com</t>
+          <t>sdcklmid@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1282,10 +1282,10 @@
         <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="R9" t="n">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1311,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스포짐 홍대서교점</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>spogym20@naver.com</t>
+          <t>yacle70@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1404-7839</t>
+          <t>0507-1340-4802</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로5나길 18 서교동 대우미래사랑 B1 101호</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym20</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>734</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>627</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>1361</v>
+        <v>100</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1025720971</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025720971</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>본소마메드짐 재활운동&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yacle70@naver.com</t>
+          <t>bornsomamedgym_mapo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1415-2855</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1447,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4j6tl</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>295</v>
       </c>
       <c r="R11" t="n">
-        <v>100</v>
+        <v>331</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>38729047</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/38729047</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1499,43 +1503,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>버핏그라운드 합정</t>
+          <t>스파인필라테스 광흥창점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>pilatescoach@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1434-3624</t>
+          <t>0507-1418-7330</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1층 111~113호</t>
+          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/place/28</t>
+          <t>https://blog.naver.com/pilatescoach</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1550,13 +1550,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4edlt</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1565,13 +1569,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>470</v>
+        <v>187</v>
       </c>
       <c r="Q12" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="R12" t="n">
-        <v>536</v>
+        <v>285</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,12 +1584,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2016796492</t>
+          <t>1285047181</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016796492</t>
+          <t>https://m.place.naver.com/place/1285047181</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1597,39 +1601,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>스파인필라테스 광흥창점</t>
+          <t>팀버핏 합정</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pilatescoach@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>jhjh5508@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1418-7330</t>
+          <t>0507-1339-3624</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
+          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1F</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatescoach</t>
+          <t>https://teambutfit.com/place/28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1644,17 +1652,13 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4edlt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1663,13 +1667,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="Q13" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>285</v>
+        <v>121</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1678,109 +1682,15 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1285047181</t>
+          <t>2003174634</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285047181</t>
+          <t>https://m.place.naver.com/place/2003174634</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GDR골프존 테리온휘트니스</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>teriongdr@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1377-6846</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>서울특별시 마포구 매봉산로 45 kbs미디어센터 지하1층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://teriongdr.wixsite.com/terionfit</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1228</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>775</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2003</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1210920885</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1210920885</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5036</v>
+        <v>5046</v>
       </c>
       <c r="Q2" t="n">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="R2" t="n">
-        <v>5694</v>
+        <v>5714</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1582</v>
+        <v>1605</v>
       </c>
       <c r="Q3" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="R3" t="n">
-        <v>1983</v>
+        <v>2010</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,11 +760,7 @@
           <t>fitnesslab_yg@naver.com</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>jmusic0921@gmail.com</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>0507-1339-5687</t>
@@ -788,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -838,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -906,10 +902,10 @@
         <v>42</v>
       </c>
       <c r="Q5" t="n">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="R5" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -928,7 +924,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +936,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MakeYourBody</t>
+          <t>좋은습관 PT STUDIO 연남</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yoda1125@naver.com</t>
+          <t>goodhabit_yeonnam@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1482-8100</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 독막로 282 지하1층</t>
+          <t>서울특별시 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yoda1125</t>
+          <t>https://blog.naver.com/goodhabit_yeonnam</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,17 +985,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>142</v>
+        <v>383</v>
       </c>
       <c r="Q6" t="n">
-        <v>274</v>
+        <v>170</v>
       </c>
       <c r="R6" t="n">
-        <v>416</v>
+        <v>553</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1728501834</t>
+          <t>1155659788</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1728501834</t>
+          <t>https://m.place.naver.com/place/1155659788</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1086,10 @@
         <v>176</v>
       </c>
       <c r="Q7" t="n">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="R7" t="n">
-        <v>634</v>
+        <v>649</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1116,7 +1108,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,44 +1120,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 상암점</t>
+          <t>다앤유재활운동센터 마포점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sdcklmid@naver.com</t>
+          <t>da-and-you@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1323-5728</t>
+          <t>0507-1344-9388</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
+          <t>서울특별시 마포구 토정로 298 3층 301호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems_sangam</t>
+          <t>https://www.daandyou.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="Q8" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="R8" t="n">
-        <v>138</v>
+        <v>230</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1405056472</t>
+          <t>1099852817</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1405056472</t>
+          <t>https://m.place.naver.com/place/1099852817</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1214,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>클럽인디고 PT 공덕역점</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>clubindi_go@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1323-6948</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 도화4길 19 2층</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://naver.me/xLWjqeVX</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1258,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>123</v>
+        <v>1133</v>
       </c>
       <c r="Q9" t="n">
-        <v>361</v>
+        <v>985</v>
       </c>
       <c r="R9" t="n">
-        <v>484</v>
+        <v>2118</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1282,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1487973827</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487973827</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>스포짐 홍대서교점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yacle70@naver.com</t>
+          <t>spogym20@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1404-7839</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울특별시 마포구 월드컵북로5나길 18 서교동 대우미래사랑 B1 101호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/spogym20</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1341,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>740</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>632</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
+        <v>1372</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>1025720971</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/1025720971</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1398,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>본소마메드짐 재활운동&amp;PT</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bornsomamedgym_mapo@naver.com</t>
+          <t>doyou56@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-2855</t>
+          <t>0507-1340-4802</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,19 +1435,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4j6tl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
-        <v>295</v>
+        <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>331</v>
+        <v>100</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,213 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38729047</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38729047</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>스파인필라테스 광흥창점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pilatescoach@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1418-7330</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/pilatescoach</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4edlt</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>187</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>98</v>
-      </c>
-      <c r="R12" t="n">
-        <v>285</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1285047181</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1285047181</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>팀버핏 합정</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>jhjh5508@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1339-3624</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1F</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://teambutfit.com/place/28</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>25</v>
-      </c>
-      <c r="R13" t="n">
-        <v>121</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2003174634</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2003174634</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5046</v>
+        <v>5048</v>
       </c>
       <c r="Q2" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="R2" t="n">
-        <v>5714</v>
+        <v>5718</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1605</v>
+        <v>1612</v>
       </c>
       <c r="Q3" t="n">
         <v>405</v>
       </c>
       <c r="R3" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,11 @@
           <t>fitnesslab_yg@naver.com</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>jmusic0921@gmail.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>0507-1339-5687</t>
@@ -784,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q4" t="n">
         <v>187</v>
       </c>
       <c r="R4" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -924,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1026,39 +1030,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT스튜디오 마포공덕점</t>
+          <t>다앤유재활운동센터 마포점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>da-and-you@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1411-7025</t>
+          <t>0507-1344-9388</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로37길 41 3층</t>
+          <t>서울특별시 마포구 토정로 298 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tndnjsqkek</t>
+          <t>https://www.daandyou.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1083,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="Q7" t="n">
-        <v>473</v>
+        <v>119</v>
       </c>
       <c r="R7" t="n">
-        <v>649</v>
+        <v>230</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1337241855</t>
+          <t>1099852817</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1337241855</t>
+          <t>https://m.place.naver.com/place/1099852817</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1120,39 +1124,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다앤유재활운동센터 마포점</t>
+          <t>턴온피트니스 PT스튜디오 마포공덕점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>da-and-you@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1344-9388</t>
+          <t>0507-1411-7025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 298 3층 301호</t>
+          <t>서울특별시 마포구 토정로37길 41 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.daandyou.com/</t>
+          <t>https://blog.naver.com/tndnjsqkek</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1177,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>119</v>
+        <v>475</v>
       </c>
       <c r="R8" t="n">
-        <v>230</v>
+        <v>651</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1099852817</t>
+          <t>1337241855</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099852817</t>
+          <t>https://m.place.naver.com/place/1337241855</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1267,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1133</v>
+        <v>1138</v>
       </c>
       <c r="Q9" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="R9" t="n">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1292,7 +1296,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1361,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Q10" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="R10" t="n">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1386,46 +1390,50 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>버핏그라운드 합정</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>doyou56@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1434-3624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1층 111~113호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.butfitground.com/place/28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1435,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1446,7 +1454,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1455,32 +1463,126 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>469</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>544</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2016796492</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2016796492</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐어웨이크PT 재활/다이어트</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>doyou56@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1340-4802</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>74</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>26</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>100</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1325649709</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 신촌로 134 지하1층 에이블짐</t>
+          <t>서울 마포구 신촌로 134 지하1층 에이블짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vqvc</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5048</v>
+        <v>5047</v>
       </c>
       <c r="Q2" t="n">
         <v>670</v>
       </c>
       <c r="R2" t="n">
-        <v>5718</v>
+        <v>5717</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 양화로 176 스타피카소 지하1층</t>
+          <t>서울 마포구 양화로 176 스타피카소 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45was</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -773,7 +781,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 266 2층 201호</t>
+          <t>서울 마포구 토정로 266 2층 201호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +806,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww7kqt9</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
+          <t>서울 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ws93zha</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -953,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 성미산로 157 지하1층</t>
+          <t>서울 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -978,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fw1e</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1047,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 298 3층 301호</t>
+          <t>서울 마포구 토정로 298 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1072,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w63v5wh</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1141,7 +1165,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로37길 41 3층</t>
+          <t>서울 마포구 토정로37길 41 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1166,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dokv</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1231,7 +1259,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
+          <t>서울 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1256,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgxg6wv</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>O</t>
@@ -1303,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스포짐 홍대서교점</t>
+          <t>짐어웨이크PT 재활\u002F다이어트</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>spogym20@naver.com</t>
+          <t>jinhee1204_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1404-7839</t>
+          <t>0507-1340-4802</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로5나길 18 서교동 대우미래사랑 B1 101호</t>
+          <t>서울 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym20</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,15 +1377,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4saqz</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1365,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>741</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>634</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>1375</v>
+        <v>100</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1025720971</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025720971</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1397,43 +1433,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 합정</t>
+          <t>본소마메드짐 재활운동&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>bornsomamedgym_mapo@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1434-3624</t>
+          <t>0507-1415-2855</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1층 111~113호</t>
+          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/place/28</t>
+          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1448,13 +1480,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4j6tl</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>469</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="R11" t="n">
-        <v>544</v>
+        <v>332</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2016796492</t>
+          <t>38729047</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016796492</t>
+          <t>https://m.place.naver.com/place/38729047</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1495,34 +1531,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>라노 필라테스 앤 피티 합정점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>doyou56@naver.com</t>
+          <t>luna951@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1418-3071</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울 마포구 양화로11길 8 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/luna951</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,15 +1573,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9etd73</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1557,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>406</v>
       </c>
       <c r="R12" t="n">
-        <v>100</v>
+        <v>501</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1612,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>1840360154</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/1840360154</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="39" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 마포구 신촌로 134 지하1층 에이블짐</t>
+          <t>서울특별시 마포구 신촌로 134 지하1층 에이블짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4vqvc</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5047</v>
+        <v>5048</v>
       </c>
       <c r="Q2" t="n">
         <v>670</v>
       </c>
       <c r="R2" t="n">
-        <v>5717</v>
+        <v>5718</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -657,44 +653,48 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 홍대점</t>
+          <t>여성전용PT 피트니스랩 용강점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthboy62@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>fitnesslab_yg@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>jmusic0921@gmail.com</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1478-1541</t>
+          <t>0507-1339-5687</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울 마포구 양화로 176 스타피카소 지하1층</t>
+          <t>서울특별시 마포구 토정로 266 2층 201호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy62/224200145779</t>
+          <t>https://booking.naver.com/booking/6/bizes/1134860</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45was</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1612</v>
+        <v>93</v>
       </c>
       <c r="Q3" t="n">
-        <v>405</v>
+        <v>187</v>
       </c>
       <c r="R3" t="n">
-        <v>2017</v>
+        <v>280</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1074811866</t>
+          <t>1003096620</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074811866</t>
+          <t>https://m.place.naver.com/place/1003096620</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,65 +751,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용PT 피트니스랩 용강점</t>
+          <t>머슬마인드PT&amp;헬스 마포공덕점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fitnesslab_yg@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>jmusic0921@gmail.com</t>
-        </is>
-      </c>
+          <t>salmonai@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1339-5687</t>
+          <t>02-706-9682</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울 마포구 토정로 266 2층 201호</t>
+          <t>서울특별시 마포구 도화길 32 상가동 지하1층 101호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1134860</t>
+          <t>https://www.instagram.com/musclemind_gongdeok/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ww7kqt9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>93</v>
+        <v>452</v>
       </c>
       <c r="Q4" t="n">
-        <v>187</v>
+        <v>1349</v>
       </c>
       <c r="R4" t="n">
-        <v>280</v>
+        <v>1801</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -840,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1003096620</t>
+          <t>1340500349</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003096620</t>
+          <t>https://m.place.naver.com/place/1340500349</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
+          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/ws93zha</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -922,10 +906,10 @@
         <v>42</v>
       </c>
       <c r="Q5" t="n">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="R5" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -969,7 +953,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울 마포구 성미산로 157 지하1층</t>
+          <t>서울특별시 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -994,14 +978,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fw1e</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1050,29 +1030,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>다앤유재활운동센터 마포점</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>da-and-you@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1344-9388</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울 마포구 토정로 298 3층 301호</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.daandyou.com/</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,27 +1058,23 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w63v5wh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>111</v>
+        <v>1138</v>
       </c>
       <c r="Q7" t="n">
-        <v>119</v>
+        <v>986</v>
       </c>
       <c r="R7" t="n">
-        <v>230</v>
+        <v>2124</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1099852817</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099852817</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1165,7 +1137,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 마포구 토정로37길 41 3층</t>
+          <t>서울특별시 마포구 토정로37길 41 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1190,14 +1162,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4dokv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1212,10 +1180,10 @@
         <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="R8" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1246,12 +1214,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT 필라테스 바디컨설팅 망원점</t>
+          <t>짐쉐이프</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>oyozz-@naver.com</t>
+          <t>lotlot1133@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1259,17 +1227,17 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 마포구 월드컵로13길 70 3층</t>
+          <t>서울특별시 마포구 독막로 262 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fdhGG/chat</t>
+          <t>https://www.instagram.com/gymshape_official</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1284,17 +1252,13 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wgxg6wv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1138</v>
+        <v>167</v>
       </c>
       <c r="Q9" t="n">
-        <v>986</v>
+        <v>152</v>
       </c>
       <c r="R9" t="n">
-        <v>2124</v>
+        <v>319</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1270971842</t>
+          <t>1243147415</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270971842</t>
+          <t>https://m.place.naver.com/place/1243147415</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1340,12 +1304,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활\u002F다이어트</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jinhee1204_@naver.com</t>
+          <t>doyou56@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1357,7 +1321,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 마포구 동교로12안길 29 2층</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1382,14 +1346,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4saqz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1433,34 +1393,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>본소마메드짐 재활운동&amp;PT</t>
+          <t>스파인필라테스 광흥창점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bornsomamedgym_mapo@naver.com</t>
+          <t>pilatescoach@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-2855</t>
+          <t>0507-1418-7330</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
+          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
+          <t>https://blog.naver.com/pilatescoach</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1445,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4j6tl</t>
+          <t>https://talk.naver.com/ct/w4edlt</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="Q11" t="n">
-        <v>296</v>
+        <v>101</v>
       </c>
       <c r="R11" t="n">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,113 +1474,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38729047</t>
+          <t>1285047181</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38729047</t>
+          <t>https://m.place.naver.com/place/1285047181</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>라노 필라테스 앤 피티 합정점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>luna951@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1418-3071</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울 마포구 양화로11길 8 5층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/luna951</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9etd73</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>406</v>
-      </c>
-      <c r="R12" t="n">
-        <v>501</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1840360154</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1840360154</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -751,34 +751,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>머슬마인드PT&amp;헬스 마포공덕점</t>
+          <t>상암동 PT 헬시온짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>salmonai@naver.com</t>
+          <t>halcyon_gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>02-706-9682</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 도화길 32 상가동 지하1층 101호</t>
+          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclemind_gongdeok/</t>
+          <t>https://www.instagram.com/halcyon_pt_studio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>452</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="n">
-        <v>1349</v>
+        <v>453</v>
       </c>
       <c r="R4" t="n">
-        <v>1801</v>
+        <v>495</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1340500349</t>
+          <t>1672818719</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340500349</t>
+          <t>https://m.place.naver.com/place/1672818719</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,12 +846,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>상암동 PT 헬시온짐</t>
+          <t>좋은습관 PT STUDIO 연남</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>halcyon_gym@naver.com</t>
+          <t>goodhabit_yeonnam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -863,12 +859,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
+          <t>서울특별시 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/halcyon_pt_studio</t>
+          <t>https://blog.naver.com/goodhabit_yeonnam</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42</v>
+        <v>383</v>
       </c>
       <c r="Q5" t="n">
-        <v>453</v>
+        <v>170</v>
       </c>
       <c r="R5" t="n">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1672818719</t>
+          <t>1155659788</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672818719</t>
+          <t>https://m.place.naver.com/place/1155659788</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 연남</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goodhabit_yeonnam@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -953,17 +949,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 성미산로 157 지하1층</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_yeonnam</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -984,7 +980,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>383</v>
+        <v>1138</v>
       </c>
       <c r="Q6" t="n">
-        <v>170</v>
+        <v>986</v>
       </c>
       <c r="R6" t="n">
-        <v>553</v>
+        <v>2124</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1004,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1155659788</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155659788</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,30 +1026,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT 필라테스 바디컨설팅 망원점</t>
+          <t>턴온피트니스 PT스튜디오 마포공덕점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oyozz-@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1411-7025</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
+          <t>서울특별시 마포구 토정로37길 41 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fdhGG/chat</t>
+          <t>https://blog.naver.com/tndnjsqkek</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1138</v>
+        <v>176</v>
       </c>
       <c r="Q7" t="n">
-        <v>986</v>
+        <v>477</v>
       </c>
       <c r="R7" t="n">
-        <v>2124</v>
+        <v>653</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1270971842</t>
+          <t>1337241855</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270971842</t>
+          <t>https://m.place.naver.com/place/1337241855</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,29 +1120,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT스튜디오 마포공덕점</t>
+          <t>짐쉐이프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>lotlot1133@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1411-7025</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로37길 41 3층</t>
+          <t>서울특별시 마포구 독막로 262 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tndnjsqkek</t>
+          <t>https://www.instagram.com/gymshape_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1153,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,13 +1173,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>477</v>
+        <v>152</v>
       </c>
       <c r="R8" t="n">
-        <v>653</v>
+        <v>319</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1188,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1337241855</t>
+          <t>1243147415</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1337241855</t>
+          <t>https://m.place.naver.com/place/1243147415</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,25 +1210,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐쉐이프</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lotlot1133@naver.com</t>
+          <t>doyou56@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1340-4802</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 독막로 262 지하1층</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymshape_official</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="Q9" t="n">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>319</v>
+        <v>100</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1243147415</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243147415</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1299,34 +1299,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>스파인필라테스 광흥창점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>doyou56@naver.com</t>
+          <t>pilatescoach@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1418-7330</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/pilatescoach</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1341,15 +1341,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4edlt</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1361,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
+        <v>293</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>1285047181</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/1285047181</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1393,34 +1397,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스파인필라테스 광흥창점</t>
+          <t>에이펙스 이엠에스 스튜디오 상암점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilatescoach@naver.com</t>
+          <t>kkokko-j@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1418-7330</t>
+          <t>0507-1323-5728</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
+          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatescoach</t>
+          <t>https://www.instagram.com/apexems_sangam</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1435,19 +1439,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4edlt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="Q11" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="R11" t="n">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,15 +1474,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1285047181</t>
+          <t>1405056472</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285047181</t>
+          <t>https://m.place.naver.com/place/1405056472</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>본소마메드짐 재활운동&amp;PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bornsomamedgym_mapo@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1415-2855</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4j6tl</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>296</v>
+      </c>
+      <c r="R12" t="n">
+        <v>332</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>38729047</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38729047</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5048</v>
+        <v>5047</v>
       </c>
       <c r="Q2" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="R2" t="n">
-        <v>5718</v>
+        <v>5719</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1198,41 +1198,41 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>스포짐 홍대서교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>doyou56@naver.com</t>
+          <t>spogym20@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1404-7839</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울특별시 마포구 월드컵북로5나길 18 서교동 대우미래사랑 B1 101호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/spogym20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>74</v>
+        <v>741</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>639</v>
       </c>
       <c r="R9" t="n">
-        <v>100</v>
+        <v>1380</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,51 +1282,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>1025720971</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/1025720971</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스파인필라테스 광흥창점</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pilatescoach@naver.com</t>
+          <t>doyou56@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1418-7330</t>
+          <t>0507-1340-4802</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatescoach</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1341,19 +1341,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4edlt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1365,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>101</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>293</v>
+        <v>100</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,56 +1376,60 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1285047181</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285047181</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 상암점</t>
+          <t>버핏그라운드 합정</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kkokko-j@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1323-5728</t>
+          <t>0507-1434-3624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
+          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1층 111~113호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems_sangam</t>
+          <t>https://www.butfitground.com/place/28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1450,7 +1450,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>469</v>
       </c>
       <c r="Q11" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="R11" t="n">
-        <v>145</v>
+        <v>544</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,51 +1474,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1405056472</t>
+          <t>2016796492</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1405056472</t>
+          <t>https://m.place.naver.com/place/2016796492</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>본소마메드짐 재활운동&amp;PT</t>
+          <t>라노 필라테스 앤 피티 합정점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bornsomamedgym_mapo@naver.com</t>
+          <t>luna951@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1415-2855</t>
+          <t>0507-1418-3071</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
+          <t>서울 마포구 양화로11길 8 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
+          <t>https://blog.naver.com/luna951</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4j6tl</t>
+          <t>https://talk.naver.com/ct/w9etd73</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>296</v>
+        <v>406</v>
       </c>
       <c r="R12" t="n">
-        <v>332</v>
+        <v>501</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>38729047</t>
+          <t>1840360154</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38729047</t>
+          <t>https://m.place.naver.com/place/1840360154</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -653,48 +653,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>여성전용PT 피트니스랩 용강점</t>
+          <t>헬스보이짐&amp;필라걸 홍대점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitnesslab_yg@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>jmusic0921@gmail.com</t>
-        </is>
-      </c>
+          <t>healthboy62@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1339-5687</t>
+          <t>0507-1478-1541</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 266 2층 201호</t>
+          <t>서울특별시 마포구 양화로 176 스타피카소 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1134860</t>
+          <t>https://blog.naver.com/healthboy62/224200145779</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -715,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>93</v>
+        <v>1612</v>
       </c>
       <c r="Q3" t="n">
-        <v>187</v>
+        <v>405</v>
       </c>
       <c r="R3" t="n">
-        <v>280</v>
+        <v>2017</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1003096620</t>
+          <t>1074811866</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003096620</t>
+          <t>https://m.place.naver.com/place/1074811866</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,40 +752,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>상암동 PT 헬시온짐</t>
+          <t>여성전용PT 피트니스랩 용강점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>halcyon_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>fitnesslab_yg@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>jmusic0921@gmail.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1339-5687</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
+          <t>서울특별시 마포구 토정로 266 2층 201호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/halcyon_pt_studio</t>
+          <t>https://booking.naver.com/booking/6/bizes/1134860</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="Q4" t="n">
-        <v>453</v>
+        <v>187</v>
       </c>
       <c r="R4" t="n">
-        <v>495</v>
+        <v>280</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1672818719</t>
+          <t>1003096620</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672818719</t>
+          <t>https://m.place.naver.com/place/1003096620</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,12 +850,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 연남</t>
+          <t>상암동 PT 헬시온짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>goodhabit_yeonnam@naver.com</t>
+          <t>halcyon_gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -859,12 +863,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 성미산로 157 지하1층</t>
+          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_yeonnam</t>
+          <t>https://www.instagram.com/halcyon_pt_studio</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>383</v>
+        <v>42</v>
       </c>
       <c r="Q5" t="n">
-        <v>170</v>
+        <v>453</v>
       </c>
       <c r="R5" t="n">
-        <v>553</v>
+        <v>495</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1155659788</t>
+          <t>1672818719</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155659788</t>
+          <t>https://m.place.naver.com/place/1672818719</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,12 +940,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT 필라테스 바디컨설팅 망원점</t>
+          <t>좋은습관 PT STUDIO 연남</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oyozz-@naver.com</t>
+          <t>goodhabit_yeonnam@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -949,17 +953,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
+          <t>서울특별시 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fdhGG/chat</t>
+          <t>https://blog.naver.com/goodhabit_yeonnam</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -969,7 +973,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -980,7 +984,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1138</v>
+        <v>383</v>
       </c>
       <c r="Q6" t="n">
-        <v>986</v>
+        <v>170</v>
       </c>
       <c r="R6" t="n">
-        <v>2124</v>
+        <v>553</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1270971842</t>
+          <t>1155659788</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270971842</t>
+          <t>https://m.place.naver.com/place/1155659788</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1026,34 +1030,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT스튜디오 마포공덕점</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1411-7025</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로37길 41 3층</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tndnjsqkek</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1074,7 +1074,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>176</v>
+        <v>1138</v>
       </c>
       <c r="Q7" t="n">
-        <v>477</v>
+        <v>986</v>
       </c>
       <c r="R7" t="n">
-        <v>653</v>
+        <v>2124</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1337241855</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1337241855</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,25 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐쉐이프</t>
+          <t>턴온피트니스 PT스튜디오 마포공덕점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lotlot1133@naver.com</t>
+          <t>tndnjsqkek@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1411-7025</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 독막로 262 지하1층</t>
+          <t>서울특별시 마포구 토정로37길 41 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymshape_official</t>
+          <t>https://blog.naver.com/tndnjsqkek</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1153,7 +1157,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1173,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>152</v>
+        <v>478</v>
       </c>
       <c r="R8" t="n">
-        <v>319</v>
+        <v>654</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1243147415</t>
+          <t>1337241855</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243147415</t>
+          <t>https://m.place.naver.com/place/1337241855</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1205,39 +1209,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>스포짐 홍대서교점</t>
+          <t>클럽인디고 PT 공덕역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spogym20@naver.com</t>
+          <t>clubindi_go@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1404-7839</t>
+          <t>0507-1323-6948</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로5나길 18 서교동 대우미래사랑 B1 101호</t>
+          <t>서울특별시 마포구 도화4길 19 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spogym20</t>
+          <t>https://naver.me/xLWjqeVX</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1247,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1267,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>741</v>
+        <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>639</v>
+        <v>335</v>
       </c>
       <c r="R9" t="n">
-        <v>1380</v>
+        <v>458</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1025720971</t>
+          <t>1487973827</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025720971</t>
+          <t>https://m.place.naver.com/place/1487973827</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1393,43 +1397,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 합정</t>
+          <t>본소마메드짐 재활운동&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>bornsomamedgym_mapo@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1434-3624</t>
+          <t>0507-1415-2855</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1층 111~113호</t>
+          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/place/28</t>
+          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1444,13 +1444,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4j6tl</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>469</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="R11" t="n">
-        <v>544</v>
+        <v>332</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,12 +1478,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2016796492</t>
+          <t>38729047</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016796492</t>
+          <t>https://m.place.naver.com/place/38729047</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1560,10 +1564,10 @@
         <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="R12" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -421,9 +421,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -624,10 +624,10 @@
         <v>5047</v>
       </c>
       <c r="Q2" t="n">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="R2" t="n">
-        <v>5719</v>
+        <v>5721</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="Q3" t="n">
         <v>405</v>
       </c>
       <c r="R3" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -752,48 +752,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>여성전용PT 피트니스랩 용강점</t>
+          <t>상암동 PT 헬시온짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fitnesslab_yg@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>jmusic0921@gmail.com</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1339-5687</t>
-        </is>
-      </c>
+          <t>halcyon_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 266 2층 201호</t>
+          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1134860</t>
+          <t>https://www.instagram.com/halcyon_pt_studio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,17 +801,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="Q4" t="n">
-        <v>187</v>
+        <v>453</v>
       </c>
       <c r="R4" t="n">
-        <v>280</v>
+        <v>495</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1003096620</t>
+          <t>1672818719</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003096620</t>
+          <t>https://m.place.naver.com/place/1672818719</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,12 +842,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>상암동 PT 헬시온짐</t>
+          <t>좋은습관 PT STUDIO 연남</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>halcyon_gym@naver.com</t>
+          <t>goodhabit_yeonnam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -863,12 +855,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
+          <t>서울특별시 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/halcyon_pt_studio</t>
+          <t>https://blog.naver.com/goodhabit_yeonnam</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,7 +875,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42</v>
+        <v>383</v>
       </c>
       <c r="Q5" t="n">
-        <v>453</v>
+        <v>170</v>
       </c>
       <c r="R5" t="n">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1672818719</t>
+          <t>1155659788</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672818719</t>
+          <t>https://m.place.naver.com/place/1155659788</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,12 +932,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 연남</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goodhabit_yeonnam@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -953,17 +945,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 성미산로 157 지하1층</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_yeonnam</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -973,7 +965,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -984,7 +976,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,13 +985,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>383</v>
+        <v>1138</v>
       </c>
       <c r="Q6" t="n">
-        <v>170</v>
+        <v>986</v>
       </c>
       <c r="R6" t="n">
-        <v>553</v>
+        <v>2124</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1000,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1155659788</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155659788</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1030,25 +1022,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT 필라테스 바디컨설팅 망원점</t>
+          <t>다앤유재활운동센터 마포점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oyozz-@naver.com</t>
+          <t>da-and-you@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1344-9388</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
+          <t>서울특별시 마포구 토정로 298 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fdhGG/chat</t>
+          <t>https://www.daandyou.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1058,12 +1054,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1074,7 +1070,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1083,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1138</v>
+        <v>111</v>
       </c>
       <c r="Q7" t="n">
-        <v>986</v>
+        <v>119</v>
       </c>
       <c r="R7" t="n">
-        <v>2124</v>
+        <v>230</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1094,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1270971842</t>
+          <t>1099852817</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270971842</t>
+          <t>https://m.place.naver.com/place/1099852817</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1120,29 +1116,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>턴온피트니스 PT스튜디오 마포공덕점</t>
+          <t>짐쉐이프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tndnjsqkek@naver.com</t>
+          <t>lotlot1133@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1411-7025</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로37길 41 3층</t>
+          <t>서울특별시 마포구 독막로 262 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tndnjsqkek</t>
+          <t>https://www.instagram.com/gymshape_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1149,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="Q8" t="n">
-        <v>478</v>
+        <v>153</v>
       </c>
       <c r="R8" t="n">
-        <v>654</v>
+        <v>320</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1337241855</t>
+          <t>1243147415</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1337241855</t>
+          <t>https://m.place.naver.com/place/1243147415</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1214,34 +1206,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>클럽인디고 PT 공덕역점</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>clubindi_go@naver.com</t>
+          <t>doyou56@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1323-6948</t>
+          <t>0507-1340-4802</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 도화4길 19 2층</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://naver.me/xLWjqeVX</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1271,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="Q9" t="n">
-        <v>335</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>458</v>
+        <v>100</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1278,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1487973827</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487973827</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,29 +1300,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>본소마메드짐 재활운동&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>doyou56@naver.com</t>
+          <t>bornsomamedgym_mapo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1415-2855</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1345,15 +1337,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4j6tl</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1365,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>296</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,12 +1376,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>38729047</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/38729047</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1397,34 +1393,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>본소마메드짐 재활운동&amp;PT</t>
+          <t>스파인필라테스 광흥창점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bornsomamedgym_mapo@naver.com</t>
+          <t>pilatescoach@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-2855</t>
+          <t>0507-1418-7330</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
+          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
+          <t>https://blog.naver.com/pilatescoach</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1449,7 +1445,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4j6tl</t>
+          <t>https://talk.naver.com/ct/w4edlt</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1463,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="Q11" t="n">
-        <v>296</v>
+        <v>102</v>
       </c>
       <c r="R11" t="n">
-        <v>332</v>
+        <v>295</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38729047</t>
+          <t>1285047181</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38729047</t>
+          <t>https://m.place.naver.com/place/1285047181</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1495,34 +1491,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>라노 필라테스 앤 피티 합정점</t>
+          <t>에이펙스 이엠에스 스튜디오 상암점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>luna951@naver.com</t>
+          <t>kkokko-j@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1418-3071</t>
+          <t>0507-1323-5728</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울 마포구 양화로11길 8 5층</t>
+          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luna951</t>
+          <t>https://www.instagram.com/apexems_sangam</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,19 +1533,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9etd73</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q12" t="n">
         <v>95</v>
       </c>
-      <c r="Q12" t="n">
-        <v>407</v>
-      </c>
       <c r="R12" t="n">
-        <v>502</v>
+        <v>145</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1840360154</t>
+          <t>1405056472</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1840360154</t>
+          <t>https://m.place.naver.com/place/1405056472</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5047</v>
+        <v>5051</v>
       </c>
       <c r="Q2" t="n">
         <v>674</v>
       </c>
       <c r="R2" t="n">
-        <v>5721</v>
+        <v>5725</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="Q3" t="n">
         <v>405</v>
       </c>
       <c r="R3" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,42 +740,46 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>상암동 PT 헬시온짐</t>
+          <t>머슬마인드PT&amp;헬스 마포공덕점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>halcyon_gym@naver.com</t>
+          <t>salmonai@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>02-706-9682</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
+          <t>서울특별시 마포구 도화길 32 상가동 지하1층 101호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/halcyon_pt_studio</t>
+          <t>https://www.instagram.com/musclemind_gongdeok/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -785,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>42</v>
+        <v>452</v>
       </c>
       <c r="Q4" t="n">
-        <v>453</v>
+        <v>1353</v>
       </c>
       <c r="R4" t="n">
-        <v>495</v>
+        <v>1805</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1672818719</t>
+          <t>1340500349</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672818719</t>
+          <t>https://m.place.naver.com/place/1340500349</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -842,12 +846,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 연남</t>
+          <t>상암동 PT 헬시온짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>goodhabit_yeonnam@naver.com</t>
+          <t>halcyon_gym@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -855,12 +859,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 성미산로 157 지하1층</t>
+          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_yeonnam</t>
+          <t>https://www.instagram.com/halcyon_pt_studio</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -875,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -895,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>383</v>
+        <v>42</v>
       </c>
       <c r="Q5" t="n">
-        <v>170</v>
+        <v>453</v>
       </c>
       <c r="R5" t="n">
-        <v>553</v>
+        <v>495</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1155659788</t>
+          <t>1672818719</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155659788</t>
+          <t>https://m.place.naver.com/place/1672818719</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -932,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT 필라테스 바디컨설팅 망원점</t>
+          <t>좋은습관 PT STUDIO 연남</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>oyozz-@naver.com</t>
+          <t>goodhabit_yeonnam@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -945,17 +949,17 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
+          <t>서울특별시 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fdhGG/chat</t>
+          <t>https://blog.naver.com/goodhabit_yeonnam</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -976,7 +980,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -985,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1138</v>
+        <v>383</v>
       </c>
       <c r="Q6" t="n">
-        <v>986</v>
+        <v>170</v>
       </c>
       <c r="R6" t="n">
-        <v>2124</v>
+        <v>553</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1270971842</t>
+          <t>1155659788</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270971842</t>
+          <t>https://m.place.naver.com/place/1155659788</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1022,29 +1026,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>다앤유재활운동센터 마포점</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>da-and-you@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1344-9388</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 298 3층 301호</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.daandyou.com/</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1070,7 +1070,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>111</v>
+        <v>1139</v>
       </c>
       <c r="Q7" t="n">
-        <v>119</v>
+        <v>986</v>
       </c>
       <c r="R7" t="n">
-        <v>230</v>
+        <v>2125</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1099852817</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099852817</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1116,40 +1116,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐쉐이프</t>
+          <t>다앤유재활운동센터 마포점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lotlot1133@naver.com</t>
+          <t>da-and-you@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1344-9388</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 독막로 262 지하1층</t>
+          <t>서울특별시 마포구 토정로 298 3층 301호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymshape_official</t>
+          <t>https://www.daandyou.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1169,13 +1173,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="Q8" t="n">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="R8" t="n">
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,17 +1188,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1243147415</t>
+          <t>1099852817</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243147415</t>
+          <t>https://m.place.naver.com/place/1099852817</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1206,29 +1210,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>짐쉐이프</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>doyou56@naver.com</t>
+          <t>lotlot1133@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1340-4802</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울특별시 마포구 독막로 262 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/gymshape_official</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="R9" t="n">
-        <v>100</v>
+        <v>321</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>1243147415</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/1243147415</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1300,29 +1300,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>본소마메드짐 재활운동&amp;PT</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bornsomamedgym_mapo@naver.com</t>
+          <t>doyou56@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1415-2855</t>
+          <t>0507-1340-4802</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1337,19 +1337,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4j6tl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1361,13 +1357,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="Q10" t="n">
-        <v>296</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>332</v>
+        <v>100</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,51 +1372,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38729047</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38729047</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스파인필라테스 광흥창점</t>
+          <t>본소마메드짐 재활운동&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilatescoach@naver.com</t>
+          <t>bornsomamedgym_mapo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1418-7330</t>
+          <t>0507-1415-2855</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
+          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilatescoach</t>
+          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1445,7 +1441,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4edlt</t>
+          <t>https://talk.naver.com/ct/w4j6tl</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1459,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="Q11" t="n">
-        <v>102</v>
+        <v>296</v>
       </c>
       <c r="R11" t="n">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1285047181</t>
+          <t>38729047</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1285047181</t>
+          <t>https://m.place.naver.com/place/38729047</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1492,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 상암점</t>
+          <t>펀짐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kkokko-j@naver.com</t>
+          <t>fun_gym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1323-5728</t>
+          <t>0507-1386-8489</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
+          <t>서울특별시 마포구 월드컵로 161 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems_sangam</t>
+          <t>https://blog.naver.com/fun_gym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1553,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="Q12" t="n">
-        <v>95</v>
+        <v>209</v>
       </c>
       <c r="R12" t="n">
-        <v>145</v>
+        <v>331</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1564,111 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1405056472</t>
+          <t>1661041333</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1405056472</t>
+          <t>https://m.place.naver.com/place/1661041333</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>엠엠티 피트니스 PT 헬스</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mmt_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1359-3889</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 마포구 큰우물로 64 3층 MMT FITNESS MAPO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://litt.ly/mmt_official</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>178</v>
+      </c>
+      <c r="R13" t="n">
+        <v>498</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1721041956</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1721041956</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5051</v>
+        <v>5054</v>
       </c>
       <c r="Q2" t="n">
         <v>674</v>
       </c>
       <c r="R2" t="n">
-        <v>5725</v>
+        <v>5728</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="Q3" t="n">
         <v>405</v>
       </c>
       <c r="R3" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -812,10 +812,10 @@
         <v>452</v>
       </c>
       <c r="Q4" t="n">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="R4" t="n">
-        <v>1805</v>
+        <v>1800</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT 필라테스 바디컨설팅 망원점</t>
+          <t>짐쉐이프</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oyozz-@naver.com</t>
+          <t>lotlot1133@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1039,17 +1039,17 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
+          <t>서울특별시 마포구 독막로 262 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fdhGG/chat</t>
+          <t>https://www.instagram.com/gymshape_official</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1070,7 +1070,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1139</v>
+        <v>167</v>
       </c>
       <c r="Q7" t="n">
-        <v>986</v>
+        <v>154</v>
       </c>
       <c r="R7" t="n">
-        <v>2125</v>
+        <v>321</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1270971842</t>
+          <t>1243147415</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270971842</t>
+          <t>https://m.place.naver.com/place/1243147415</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1116,29 +1116,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다앤유재활운동센터 마포점</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>da-and-you@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1344-9388</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 298 3층 301호</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.daandyou.com/</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1148,12 +1144,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1164,7 +1160,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1173,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>111</v>
+        <v>1141</v>
       </c>
       <c r="Q8" t="n">
-        <v>119</v>
+        <v>986</v>
       </c>
       <c r="R8" t="n">
-        <v>230</v>
+        <v>2127</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1099852817</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099852817</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1210,40 +1206,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐쉐이프</t>
+          <t>다앤유재활운동센터 마포점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lotlot1133@naver.com</t>
+          <t>da-and-you@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1344-9388</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 독막로 262 지하1층</t>
+          <t>서울특별시 마포구 토정로 298 3층 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymshape_official</t>
+          <t>https://www.daandyou.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="Q9" t="n">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="R9" t="n">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1243147415</t>
+          <t>1099852817</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243147415</t>
+          <t>https://m.place.naver.com/place/1099852817</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>doyou56@naver.com</t>
+          <t>yacle70@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1487,34 +1487,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>펀짐</t>
+          <t>핏인라이프 필라테스&amp;PT 마포공덕점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fun_gym@naver.com</t>
+          <t>fitinlife@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1386-8489</t>
+          <t>0507-1338-8976</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로 161 3층</t>
+          <t>서울 마포구 토정로31길 63 지하 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fun_gym</t>
+          <t>https://blog.naver.com/fitinlife</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1534,10 +1534,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t442l</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1549,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>122</v>
+        <v>357</v>
       </c>
       <c r="Q12" t="n">
-        <v>209</v>
+        <v>870</v>
       </c>
       <c r="R12" t="n">
-        <v>331</v>
+        <v>1227</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,12 +1568,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1661041333</t>
+          <t>1212427738</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1661041333</t>
+          <t>https://m.place.naver.com/place/1212427738</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1586,34 +1590,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엠엠티 피트니스 PT 헬스</t>
+          <t>에이펙스 이엠에스 스튜디오 상암점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mmt_studio@naver.com</t>
+          <t>sdcklmid@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1359-3889</t>
+          <t>0507-1323-5728</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 큰우물로 64 3층 MMT FITNESS MAPO</t>
+          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://litt.ly/mmt_official</t>
+          <t>https://www.instagram.com/apexems_sangam</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1643,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>320</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
-        <v>178</v>
+        <v>98</v>
       </c>
       <c r="R13" t="n">
-        <v>498</v>
+        <v>148</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,12 +1662,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1721041956</t>
+          <t>1405056472</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721041956</t>
+          <t>https://m.place.naver.com/place/1405056472</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5054</v>
+        <v>5053</v>
       </c>
       <c r="Q2" t="n">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="R2" t="n">
-        <v>5728</v>
+        <v>5725</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="Q3" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -812,10 +812,10 @@
         <v>452</v>
       </c>
       <c r="Q4" t="n">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="R4" t="n">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1382,46 +1382,50 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>본소마메드짐 재활운동&amp;PT</t>
+          <t>버핏그라운드 합정</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bornsomamedgym_mapo@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1415-2855</t>
+          <t>0507-1434-3624</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
+          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1층 111~113호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
+          <t>https://www.butfitground.com/place/28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1436,17 +1440,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4j6tl</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>36</v>
+        <v>469</v>
       </c>
       <c r="Q11" t="n">
-        <v>296</v>
+        <v>76</v>
       </c>
       <c r="R11" t="n">
-        <v>332</v>
+        <v>545</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>38729047</t>
+          <t>2016796492</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38729047</t>
+          <t>https://m.place.naver.com/place/2016796492</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1492,29 +1492,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>핏인라이프 필라테스&amp;PT 마포공덕점</t>
+          <t>스파인필라테스 광흥창점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fitinlife@naver.com</t>
+          <t>pilatescoach@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1338-8976</t>
+          <t>0507-1418-7330</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울 마포구 토정로31길 63 지하 1층</t>
+          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitinlife</t>
+          <t>https://blog.naver.com/pilatescoach</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t442l</t>
+          <t>https://talk.naver.com/ct/w4edlt</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>357</v>
+        <v>193</v>
       </c>
       <c r="Q12" t="n">
-        <v>870</v>
+        <v>103</v>
       </c>
       <c r="R12" t="n">
-        <v>1227</v>
+        <v>296</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,111 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1212427738</t>
+          <t>1285047181</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1212427738</t>
+          <t>https://m.place.naver.com/place/1285047181</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>에이펙스 이엠에스 스튜디오 상암점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>sdcklmid@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1323-5728</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/apexems_sangam</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>98</v>
-      </c>
-      <c r="R13" t="n">
-        <v>148</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1405056472</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1405056472</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/마포_PT.xlsx
+++ b/naver-place-crawler/results_health/마포_PT.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -559,34 +559,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이블짐 신촌점</t>
+          <t>상암동 PT 헬시온짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ablegymfit17@naver.com</t>
+          <t>halcyon_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1318-3455</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 신촌로 134 지하1층 에이블짐</t>
+          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ablegymfit17/224139428821</t>
+          <t>https://www.instagram.com/halcyon_pt_studio</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +608,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>5053</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="n">
-        <v>672</v>
+        <v>453</v>
       </c>
       <c r="R2" t="n">
-        <v>5725</v>
+        <v>495</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +632,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1429980657</t>
+          <t>1672818719</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429980657</t>
+          <t>https://m.place.naver.com/place/1672818719</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +649,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 홍대점</t>
+          <t>좋은습관 PT STUDIO 연남</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthboy62@naver.com</t>
+          <t>goodhabit_yeonnam@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1478-1541</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 양화로 176 스타피카소 지하1층</t>
+          <t>서울특별시 마포구 성미산로 157 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy62/224200145779</t>
+          <t>https://blog.naver.com/goodhabit_yeonnam</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +707,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1617</v>
+        <v>383</v>
       </c>
       <c r="Q3" t="n">
-        <v>404</v>
+        <v>170</v>
       </c>
       <c r="R3" t="n">
-        <v>2021</v>
+        <v>553</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +722,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1074811866</t>
+          <t>1155659788</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1074811866</t>
+          <t>https://m.place.naver.com/place/1155659788</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +739,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>머슬마인드PT&amp;헬스 마포공덕점</t>
+          <t>짐쉐이프</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>salmonai@naver.com</t>
+          <t>lotlot1133@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>02-706-9682</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 도화길 32 상가동 지하1층 101호</t>
+          <t>서울특별시 마포구 독막로 262 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclemind_gongdeok/</t>
+          <t>https://www.instagram.com/gymshape_official</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +797,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>452</v>
+        <v>167</v>
       </c>
       <c r="Q4" t="n">
-        <v>1347</v>
+        <v>154</v>
       </c>
       <c r="R4" t="n">
-        <v>1799</v>
+        <v>321</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +812,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1340500349</t>
+          <t>1243147415</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340500349</t>
+          <t>https://m.place.naver.com/place/1243147415</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,12 +834,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>상암동 PT 헬시온짐</t>
+          <t>PT 필라테스 바디컨설팅 망원점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>halcyon_gym@naver.com</t>
+          <t>oyozz-@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -859,17 +847,17 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵북로54길 17 B동 3층 304,305,307호</t>
+          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/halcyon_pt_studio</t>
+          <t>http://pf.kakao.com/_fdhGG/chat</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -890,7 +878,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -899,13 +887,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>42</v>
+        <v>1141</v>
       </c>
       <c r="Q5" t="n">
-        <v>453</v>
+        <v>986</v>
       </c>
       <c r="R5" t="n">
-        <v>495</v>
+        <v>2127</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1672818719</t>
+          <t>1270971842</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672818719</t>
+          <t>https://m.place.naver.com/place/1270971842</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -936,35 +924,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>좋은습관 PT STUDIO 연남</t>
+          <t>다앤유재활운동센터 마포점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goodhabit_yeonnam@naver.com</t>
+          <t>da-and-you@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1344-9388</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 성미산로 157 지하1층</t>
+          <t>서울특별시 마포구 토정로 298 3층 301호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodhabit_yeonnam</t>
+          <t>https://www.daandyou.com/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -989,13 +981,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>383</v>
+        <v>111</v>
       </c>
       <c r="Q6" t="n">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="R6" t="n">
-        <v>553</v>
+        <v>230</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,12 +996,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1155659788</t>
+          <t>1099852817</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1155659788</t>
+          <t>https://m.place.naver.com/place/1099852817</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1026,25 +1018,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐쉐이프</t>
+          <t>짐어웨이크PT 재활/다이어트</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lotlot1133@naver.com</t>
+          <t>yacle70@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1340-4802</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 독막로 262 지하1층</t>
+          <t>서울특별시 마포구 동교로12안길 29 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymshape_official</t>
+          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,13 +1075,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="Q7" t="n">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="R7" t="n">
-        <v>321</v>
+        <v>100</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,12 +1090,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1243147415</t>
+          <t>1325649709</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243147415</t>
+          <t>https://m.place.naver.com/place/1325649709</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1116,30 +1112,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT 필라테스 바디컨설팅 망원점</t>
+          <t>에이펙스 이엠에스 스튜디오 상암점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>oyozz-@naver.com</t>
+          <t>sdcklmid@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1323-5728</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 월드컵로13길 70 3층</t>
+          <t>서울특별시 마포구 월드컵북로 434 1층 121호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_fdhGG/chat</t>
+          <t>https://www.instagram.com/apexems_sangam</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1141</v>
+        <v>51</v>
       </c>
       <c r="Q8" t="n">
-        <v>986</v>
+        <v>98</v>
       </c>
       <c r="R8" t="n">
-        <v>2127</v>
+        <v>149</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1270971842</t>
+          <t>1405056472</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1270971842</t>
+          <t>https://m.place.naver.com/place/1405056472</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1206,39 +1206,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>다앤유재활운동센터 마포점</t>
+          <t>본소마메드짐 재활운동&amp;PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>da-and-you@naver.com</t>
+          <t>bornsomamedgym_mapo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1344-9388</t>
+          <t>0507-1415-2855</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 토정로 298 3층 301호</t>
+          <t>서울 마포구 큰우물로 52 세일종합상가 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.daandyou.com/</t>
+          <t>https://blog.naver.com/bornsomamedgym_mapo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1248,10 +1248,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4j6tl</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1263,13 +1267,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="n">
-        <v>119</v>
+        <v>296</v>
       </c>
       <c r="R9" t="n">
-        <v>230</v>
+        <v>332</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,12 +1282,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1099852817</t>
+          <t>38729047</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1099852817</t>
+          <t>https://m.place.naver.com/place/38729047</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1300,29 +1304,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>짐어웨이크PT 재활/다이어트</t>
+          <t>펀짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yacle70@naver.com</t>
+          <t>fun_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1340-4802</t>
+          <t>0507-1386-8489</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 동교로12안길 29 2층</t>
+          <t>서울특별시 마포구 월드컵로 161 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_awake.official/?igshid=NGVhN2U2NjQ0Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/fun_gym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1337,7 +1341,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1357,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="R10" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1372,12 +1376,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1325649709</t>
+          <t>1661041333</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1325649709</t>
+          <t>https://m.place.naver.com/place/1661041333</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1389,38 +1393,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 합정</t>
+          <t>엠엠티 피트니스 PT 헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>mmt_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1434-3624</t>
+          <t>0507-1359-3889</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 마포구 양화로 45 메세나폴리스 B1층 111~113호</t>
+          <t>서울특별시 마포구 큰우물로 64 3층 MMT FITNESS MAPO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/place/28</t>
+          <t>https://litt.ly/mmt_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1446,7 +1446,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1455,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>469</v>
+        <v>320</v>
       </c>
       <c r="Q11" t="n">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="R11" t="n">
-        <v>545</v>
+        <v>498</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,113 +1470,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2016796492</t>
+          <t>1721041956</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016796492</t>
+          <t>https://m.place.naver.com/place/1721041956</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>스파인필라테스 광흥창점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pilatescoach@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1418-7330</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>서울 마포구 독막로 168 한도빌딩 3층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/pilatescoach</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4edlt</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>193</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>103</v>
-      </c>
-      <c r="R12" t="n">
-        <v>296</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1285047181</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1285047181</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
